--- a/data/nzd0600/nzd0600.xlsx
+++ b/data/nzd0600/nzd0600.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H625"/>
+  <dimension ref="A1:H628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19180,6 +19180,96 @@
         <v>213.08</v>
       </c>
       <c r="H625" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>220.27</v>
+      </c>
+      <c r="C626" t="n">
+        <v>216.28</v>
+      </c>
+      <c r="D626" t="n">
+        <v>217.3</v>
+      </c>
+      <c r="E626" t="n">
+        <v>223.71</v>
+      </c>
+      <c r="F626" t="n">
+        <v>222.57</v>
+      </c>
+      <c r="G626" t="n">
+        <v>212.61</v>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>221.3</v>
+      </c>
+      <c r="C627" t="n">
+        <v>214.59</v>
+      </c>
+      <c r="D627" t="n">
+        <v>215.63</v>
+      </c>
+      <c r="E627" t="n">
+        <v>224.76</v>
+      </c>
+      <c r="F627" t="n">
+        <v>222.21</v>
+      </c>
+      <c r="G627" t="n">
+        <v>211.89</v>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>220.06</v>
+      </c>
+      <c r="C628" t="n">
+        <v>213.28</v>
+      </c>
+      <c r="D628" t="n">
+        <v>215.63</v>
+      </c>
+      <c r="E628" t="n">
+        <v>223.52</v>
+      </c>
+      <c r="F628" t="n">
+        <v>220.21</v>
+      </c>
+      <c r="G628" t="n">
+        <v>211.29</v>
+      </c>
+      <c r="H628" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19196,7 +19286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B736"/>
+  <dimension ref="A1:B740"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26559,6 +26649,46 @@
       </c>
       <c r="B736" t="n">
         <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>-0.31</v>
       </c>
     </row>
   </sheetData>
@@ -26721,28 +26851,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1976345874690168</v>
+        <v>-0.2058615250563836</v>
       </c>
       <c r="J2" t="n">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="K2" t="n">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03147112519186712</v>
+        <v>0.03420716584534311</v>
       </c>
       <c r="M2" t="n">
-        <v>5.847349498171225</v>
+        <v>5.853386084723115</v>
       </c>
       <c r="N2" t="n">
-        <v>53.84507015533965</v>
+        <v>53.8864594399261</v>
       </c>
       <c r="O2" t="n">
-        <v>7.337920015599765</v>
+        <v>7.340739706591298</v>
       </c>
       <c r="P2" t="n">
-        <v>233.8216304834642</v>
+        <v>233.9253660814118</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26793,28 +26923,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5274842753648146</v>
+        <v>-0.5324125111743735</v>
       </c>
       <c r="J3" t="n">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="K3" t="n">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2148701948269053</v>
+        <v>0.2193367826038309</v>
       </c>
       <c r="M3" t="n">
-        <v>5.502257083789459</v>
+        <v>5.494538801960418</v>
       </c>
       <c r="N3" t="n">
-        <v>45.54115739268722</v>
+        <v>45.43715659198234</v>
       </c>
       <c r="O3" t="n">
-        <v>6.748418880944426</v>
+        <v>6.740708908711482</v>
       </c>
       <c r="P3" t="n">
-        <v>233.7078899550805</v>
+        <v>233.7700372868783</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26865,28 +26995,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1806152585301324</v>
+        <v>0.1761820462621658</v>
       </c>
       <c r="J4" t="n">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="K4" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04099665234626759</v>
+        <v>0.03937141656194654</v>
       </c>
       <c r="M4" t="n">
-        <v>4.400078135161849</v>
+        <v>4.398543519370366</v>
       </c>
       <c r="N4" t="n">
-        <v>34.17992166232777</v>
+        <v>34.10554595172368</v>
       </c>
       <c r="O4" t="n">
-        <v>5.846359693204633</v>
+        <v>5.839995372577248</v>
       </c>
       <c r="P4" t="n">
-        <v>215.5930376700899</v>
+        <v>215.6489685525308</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26937,28 +27067,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4024713318088057</v>
+        <v>0.4006879245714817</v>
       </c>
       <c r="J5" t="n">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="K5" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1195508633968185</v>
+        <v>0.119663587592406</v>
       </c>
       <c r="M5" t="n">
-        <v>5.434949746271963</v>
+        <v>5.41608052567349</v>
       </c>
       <c r="N5" t="n">
-        <v>52.95634088550804</v>
+        <v>52.71776642676215</v>
       </c>
       <c r="O5" t="n">
-        <v>7.277110751219061</v>
+        <v>7.260700133372962</v>
       </c>
       <c r="P5" t="n">
-        <v>214.8454199684474</v>
+        <v>214.8680066042549</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27009,28 +27139,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3248850556904065</v>
+        <v>0.3311676124592907</v>
       </c>
       <c r="J6" t="n">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="K6" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04712009797359806</v>
+        <v>0.0492608308102791</v>
       </c>
       <c r="M6" t="n">
-        <v>7.474842617591261</v>
+        <v>7.469771699532311</v>
       </c>
       <c r="N6" t="n">
-        <v>94.75190804894083</v>
+        <v>94.47419824046573</v>
       </c>
       <c r="O6" t="n">
-        <v>9.73405917636321</v>
+        <v>9.719783857703097</v>
       </c>
       <c r="P6" t="n">
-        <v>206.8765954733237</v>
+        <v>206.797028805913</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27081,28 +27211,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1835741011656172</v>
+        <v>-0.1794636798991912</v>
       </c>
       <c r="J7" t="n">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="K7" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05659503887525397</v>
+        <v>0.05459719709357813</v>
       </c>
       <c r="M7" t="n">
-        <v>3.95173240107665</v>
+        <v>3.950630760290873</v>
       </c>
       <c r="N7" t="n">
-        <v>24.93670838210521</v>
+        <v>24.89186986723421</v>
       </c>
       <c r="O7" t="n">
-        <v>4.99366682730288</v>
+        <v>4.989175269243827</v>
       </c>
       <c r="P7" t="n">
-        <v>212.9430197609856</v>
+        <v>212.8909626445068</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27140,7 +27270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H625"/>
+  <dimension ref="A1:H628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53377,6 +53507,132 @@
         </is>
       </c>
     </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>-36.89446895352892,174.98822889702404</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>-36.8951855379787,174.9881205561751</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>-36.89587583901251,174.98791831099192</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>-36.896533191225565,174.98761301493576</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>-36.897213424498425,174.9873158523666</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>-36.897900638469004,174.98707164088836</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>-36.89446737592177,174.98821750945737</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>-36.895188120401336,174.98813924210893</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>-36.89587950117275,174.98793648404074</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>-36.89652993497448,174.9876019541331</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>-36.897214541967166,174.98731964420125</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>-36.897903245159775,174.98707903837405</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>-36.89446927517685,174.988231218761</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>-36.89519012215885,174.98815372647263</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>-36.89587950117275,174.98793648404074</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>-36.89653378045184,174.98761501641442</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>-36.89722075012459,174.98734070995107</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>-36.89790541740172,174.9870852029458</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0600/nzd0600.xlsx
+++ b/data/nzd0600/nzd0600.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H628"/>
+  <dimension ref="A1:H632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19270,6 +19270,126 @@
         <v>211.29</v>
       </c>
       <c r="H628" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>224.79</v>
+      </c>
+      <c r="C629" t="n">
+        <v>213.54</v>
+      </c>
+      <c r="D629" t="n">
+        <v>217.94</v>
+      </c>
+      <c r="E629" t="n">
+        <v>226.4</v>
+      </c>
+      <c r="F629" t="n">
+        <v>223.86</v>
+      </c>
+      <c r="G629" t="n">
+        <v>211.31</v>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>227.67</v>
+      </c>
+      <c r="C630" t="n">
+        <v>213.54</v>
+      </c>
+      <c r="D630" t="n">
+        <v>219.44</v>
+      </c>
+      <c r="E630" t="n">
+        <v>227.06</v>
+      </c>
+      <c r="F630" t="n">
+        <v>224.96</v>
+      </c>
+      <c r="G630" t="n">
+        <v>211.82</v>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:53+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>226.4</v>
+      </c>
+      <c r="C631" t="n">
+        <v>211.26</v>
+      </c>
+      <c r="D631" t="n">
+        <v>219.44</v>
+      </c>
+      <c r="E631" t="n">
+        <v>226.49</v>
+      </c>
+      <c r="F631" t="n">
+        <v>223.61</v>
+      </c>
+      <c r="G631" t="n">
+        <v>214.21</v>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>226.62</v>
+      </c>
+      <c r="C632" t="n">
+        <v>211.45</v>
+      </c>
+      <c r="D632" t="n">
+        <v>220.57</v>
+      </c>
+      <c r="E632" t="n">
+        <v>225.68</v>
+      </c>
+      <c r="F632" t="n">
+        <v>222.84</v>
+      </c>
+      <c r="G632" t="n">
+        <v>214.6</v>
+      </c>
+      <c r="H632" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19286,7 +19406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B740"/>
+  <dimension ref="A1:B744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26689,6 +26809,46 @@
       </c>
       <c r="B740" t="n">
         <v>-0.31</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -26851,28 +27011,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2058615250563836</v>
+        <v>-0.2085700190188133</v>
       </c>
       <c r="J2" t="n">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="K2" t="n">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03420716584534311</v>
+        <v>0.03552209493444469</v>
       </c>
       <c r="M2" t="n">
-        <v>5.853386084723115</v>
+        <v>5.827528242675217</v>
       </c>
       <c r="N2" t="n">
-        <v>53.8864594399261</v>
+        <v>53.57611875108233</v>
       </c>
       <c r="O2" t="n">
-        <v>7.340739706591298</v>
+        <v>7.31957094036818</v>
       </c>
       <c r="P2" t="n">
-        <v>233.9253660814118</v>
+        <v>233.9596240240001</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26923,28 +27083,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5324125111743735</v>
+        <v>-0.5418592727045111</v>
       </c>
       <c r="J3" t="n">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="K3" t="n">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2193367826038309</v>
+        <v>0.2266091645320634</v>
       </c>
       <c r="M3" t="n">
-        <v>5.494538801960418</v>
+        <v>5.49530369896799</v>
       </c>
       <c r="N3" t="n">
-        <v>45.43715659198234</v>
+        <v>45.45360630607711</v>
       </c>
       <c r="O3" t="n">
-        <v>6.740708908711482</v>
+        <v>6.741928975158156</v>
       </c>
       <c r="P3" t="n">
-        <v>233.7700372868783</v>
+        <v>233.8895705473603</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26995,28 +27155,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1761820462621658</v>
+        <v>0.1747211423187229</v>
       </c>
       <c r="J4" t="n">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="K4" t="n">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03937141656194654</v>
+        <v>0.03923890580893097</v>
       </c>
       <c r="M4" t="n">
-        <v>4.398543519370366</v>
+        <v>4.37760588151793</v>
       </c>
       <c r="N4" t="n">
-        <v>34.10554595172368</v>
+        <v>33.90161287452057</v>
       </c>
       <c r="O4" t="n">
-        <v>5.839995372577248</v>
+        <v>5.822509156241884</v>
       </c>
       <c r="P4" t="n">
-        <v>215.6489685525308</v>
+        <v>215.6674420355413</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27067,28 +27227,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4006879245714817</v>
+        <v>0.4016415041183503</v>
       </c>
       <c r="J5" t="n">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="K5" t="n">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="L5" t="n">
-        <v>0.119663587592406</v>
+        <v>0.1216002772844468</v>
       </c>
       <c r="M5" t="n">
-        <v>5.41608052567349</v>
+        <v>5.386753565642751</v>
       </c>
       <c r="N5" t="n">
-        <v>52.71776642676215</v>
+        <v>52.38762360615149</v>
       </c>
       <c r="O5" t="n">
-        <v>7.260700133372962</v>
+        <v>7.237929510996324</v>
       </c>
       <c r="P5" t="n">
-        <v>214.8680066042549</v>
+        <v>214.8558969797166</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27139,28 +27299,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3311676124592907</v>
+        <v>0.3422552423174528</v>
       </c>
       <c r="J6" t="n">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="K6" t="n">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0492608308102791</v>
+        <v>0.05290052361342601</v>
       </c>
       <c r="M6" t="n">
-        <v>7.469771699532311</v>
+        <v>7.477121202518024</v>
       </c>
       <c r="N6" t="n">
-        <v>94.47419824046573</v>
+        <v>94.28220866782434</v>
       </c>
       <c r="O6" t="n">
-        <v>9.719783857703097</v>
+        <v>9.709902608565358</v>
       </c>
       <c r="P6" t="n">
-        <v>206.797028805913</v>
+        <v>206.6561470886451</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27211,28 +27371,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1794636798991912</v>
+        <v>-0.172643280479382</v>
       </c>
       <c r="J7" t="n">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="K7" t="n">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05459719709357813</v>
+        <v>0.05106659248322709</v>
       </c>
       <c r="M7" t="n">
-        <v>3.950630760290873</v>
+        <v>3.954763167668865</v>
       </c>
       <c r="N7" t="n">
-        <v>24.89186986723421</v>
+        <v>24.89958565303003</v>
       </c>
       <c r="O7" t="n">
-        <v>4.989175269243827</v>
+        <v>4.989948461961308</v>
       </c>
       <c r="P7" t="n">
-        <v>212.8909626445068</v>
+        <v>212.8042670073096</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27270,7 +27430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H628"/>
+  <dimension ref="A1:H632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53633,6 +53793,174 @@
         </is>
       </c>
     </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>-36.89446203042908,174.98817892440437</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>-36.89518972486361,174.98815085171339</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>-36.89587443554915,174.98791134647064</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>-36.896524849018306,174.98758467821457</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>-36.897209420234404,174.9873022649601</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>-36.89790534499365,174.98708499746007</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>-36.89445761923931,174.98814708344733</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>-36.89518972486361,174.98815085171339</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>-36.89587114618027,174.98789502337482</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>-36.896522802230336,174.9875777257114</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>-36.89720600574444,174.98729067880058</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>-36.897903498588015,174.98707975757407</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:53+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>-36.89445956445253,174.9881611244245</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>-36.89519320883487,174.98817606114162</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>-36.89587114618027,174.98789502337482</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>-36.89652456991089,174.98758373014593</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>-36.8972101962547,174.9873048981783</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>-36.897894845821135,174.98705520203308</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>-36.894459227486585,174.98815869212922</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>-36.89519291850414,174.98817396035585</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>-36.89586866818753,174.9878827266435</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>-36.896527081877444,174.9875922627639</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>-36.89721258639678,174.98731300849073</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>-36.897893433862855,174.98705119506246</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0600/nzd0600.xlsx
+++ b/data/nzd0600/nzd0600.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H632"/>
+  <dimension ref="A1:H634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19282,7 +19282,7 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>224.79</v>
+        <v>220.06</v>
       </c>
       <c r="C629" t="n">
         <v>213.54</v>
@@ -19312,7 +19312,7 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>227.67</v>
+        <v>220.06</v>
       </c>
       <c r="C630" t="n">
         <v>213.54</v>
@@ -19342,7 +19342,7 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>226.4</v>
+        <v>217.95</v>
       </c>
       <c r="C631" t="n">
         <v>211.26</v>
@@ -19372,7 +19372,7 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>226.62</v>
+        <v>218.2</v>
       </c>
       <c r="C632" t="n">
         <v>211.45</v>
@@ -19387,11 +19387,71 @@
         <v>222.84</v>
       </c>
       <c r="G632" t="n">
-        <v>214.6</v>
+        <v>214.96</v>
       </c>
       <c r="H632" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>218.2</v>
+      </c>
+      <c r="C633" t="n">
+        <v>211.45</v>
+      </c>
+      <c r="D633" t="n">
+        <v>220.57</v>
+      </c>
+      <c r="E633" t="n">
+        <v>225.68</v>
+      </c>
+      <c r="F633" t="n">
+        <v>231.76</v>
+      </c>
+      <c r="G633" t="n">
+        <v>222.51</v>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>219.4</v>
+      </c>
+      <c r="C634" t="n">
+        <v>212.16</v>
+      </c>
+      <c r="D634" t="n">
+        <v>220.57</v>
+      </c>
+      <c r="E634" t="n">
+        <v>217.99</v>
+      </c>
+      <c r="F634" t="n">
+        <v>242.35</v>
+      </c>
+      <c r="G634" t="n">
+        <v>231.56</v>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -19406,7 +19466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B744"/>
+  <dimension ref="A1:B746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26849,6 +26909,26 @@
       </c>
       <c r="B744" t="n">
         <v>0.61</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>
@@ -27011,28 +27091,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2085700190188133</v>
+        <v>-0.2249201460346543</v>
       </c>
       <c r="J2" t="n">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="K2" t="n">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03552209493444469</v>
+        <v>0.04076463098720451</v>
       </c>
       <c r="M2" t="n">
-        <v>5.827528242675217</v>
+        <v>5.877294630626276</v>
       </c>
       <c r="N2" t="n">
-        <v>53.57611875108233</v>
+        <v>54.19068276865714</v>
       </c>
       <c r="O2" t="n">
-        <v>7.31957094036818</v>
+        <v>7.36143211397464</v>
       </c>
       <c r="P2" t="n">
-        <v>233.9596240240001</v>
+        <v>234.1667401882987</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27083,28 +27163,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5418592727045111</v>
+        <v>-0.5468860479176527</v>
       </c>
       <c r="J3" t="n">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="K3" t="n">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2266091645320634</v>
+        <v>0.2303905911249308</v>
       </c>
       <c r="M3" t="n">
-        <v>5.49530369896799</v>
+        <v>5.497030471049952</v>
       </c>
       <c r="N3" t="n">
-        <v>45.45360630607711</v>
+        <v>45.48053429608838</v>
       </c>
       <c r="O3" t="n">
-        <v>6.741928975158156</v>
+        <v>6.743925733286836</v>
       </c>
       <c r="P3" t="n">
-        <v>233.8895705473603</v>
+        <v>233.9533550136739</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27155,28 +27235,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1747211423187229</v>
+        <v>0.1748272816614982</v>
       </c>
       <c r="J4" t="n">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="K4" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03923890580893097</v>
+        <v>0.03953963330870136</v>
       </c>
       <c r="M4" t="n">
-        <v>4.37760588151793</v>
+        <v>4.364254379092094</v>
       </c>
       <c r="N4" t="n">
-        <v>33.90161287452057</v>
+        <v>33.7944051782106</v>
       </c>
       <c r="O4" t="n">
-        <v>5.822509156241884</v>
+        <v>5.813295552284488</v>
       </c>
       <c r="P4" t="n">
-        <v>215.6674420355413</v>
+        <v>215.6660945491418</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27227,28 +27307,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4016415041183503</v>
+        <v>0.3989434773299428</v>
       </c>
       <c r="J5" t="n">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="K5" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1216002772844468</v>
+        <v>0.1206922383478697</v>
       </c>
       <c r="M5" t="n">
-        <v>5.386753565642751</v>
+        <v>5.380641628502961</v>
       </c>
       <c r="N5" t="n">
-        <v>52.38762360615149</v>
+        <v>52.31701126887969</v>
       </c>
       <c r="O5" t="n">
-        <v>7.237929510996324</v>
+        <v>7.233049928548792</v>
       </c>
       <c r="P5" t="n">
-        <v>214.8558969797166</v>
+        <v>214.8902965395416</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27299,28 +27379,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3422552423174528</v>
+        <v>0.3567608340149104</v>
       </c>
       <c r="J6" t="n">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="K6" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05290052361342601</v>
+        <v>0.05673920820725942</v>
       </c>
       <c r="M6" t="n">
-        <v>7.477121202518024</v>
+        <v>7.526056658542921</v>
       </c>
       <c r="N6" t="n">
-        <v>94.28220866782434</v>
+        <v>95.46880272629731</v>
       </c>
       <c r="O6" t="n">
-        <v>9.709902608565358</v>
+        <v>9.770813821084573</v>
       </c>
       <c r="P6" t="n">
-        <v>206.6561470886451</v>
+        <v>206.4712568489678</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27371,28 +27451,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.172643280479382</v>
+        <v>-0.1595187288167703</v>
       </c>
       <c r="J7" t="n">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="K7" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05106659248322709</v>
+        <v>0.04226783266720524</v>
       </c>
       <c r="M7" t="n">
-        <v>3.954763167668865</v>
+        <v>3.998617809212951</v>
       </c>
       <c r="N7" t="n">
-        <v>24.89958565303003</v>
+        <v>26.01453566392615</v>
       </c>
       <c r="O7" t="n">
-        <v>4.989948461961308</v>
+        <v>5.100444653549938</v>
       </c>
       <c r="P7" t="n">
-        <v>212.8042670073096</v>
+        <v>212.6369823963611</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27430,7 +27510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H632"/>
+  <dimension ref="A1:H634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53801,7 +53881,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>-36.89446203042908,174.98817892440437</t>
+          <t>-36.89446927517685,174.988231218761</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -53843,7 +53923,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>-36.89445761923931,174.98814708344733</t>
+          <t>-36.89446927517685,174.988231218761</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -53885,7 +53965,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>-36.89445956445253,174.9881611244245</t>
+          <t>-36.89447250697013,174.9882545466904</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -53927,7 +54007,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>-36.894459227486585,174.98815869212922</t>
+          <t>-36.89447212405647,174.98825178271764</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -53952,12 +54032,96 @@
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>-36.897893433862855,174.98705119506246</t>
+          <t>-36.89789213051663,174.9870474963205</t>
         </is>
       </c>
       <c r="H632" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>-36.89447212405647,174.98825178271764</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>-36.89519291850414,174.98817396035585</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>-36.89586866818753,174.9878827266435</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>-36.896527081877444,174.9875922627639</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>-36.89718489796248,174.98721905529084</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>-36.89786479642251,174.9869699255098</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>-36.894470286070046,174.98823851564867</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>-36.895191833583716,174.98816611005128</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>-36.89586866818753,174.9878827266435</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>-36.89655093002234,174.98767326999075</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>-36.89715202560764,174.9871075122825</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>-36.897832031644555,174.9868769433503</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
